--- a/data-sources/International List of Pokémon Names.xlsx
+++ b/data-sources/International List of Pokémon Names.xlsx
@@ -13420,7 +13420,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Houndoor</t>
+          <t>Houndour</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13440,12 +13440,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Houndoor</t>
+          <t>Houndour</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Houndoor</t>
+          <t>Houndour</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Tailow</t>
+          <t>Taillow</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -16176,12 +16176,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tailow</t>
+          <t>Taillow</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Tailow</t>
+          <t>Taillow</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Minum</t>
+          <t>Minun</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18228,12 +18228,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Minum</t>
+          <t>Minun</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Minum</t>
+          <t>Minun</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -31489,7 +31489,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Scoliopede</t>
+          <t>Scolipede</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -31509,12 +31509,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Scoliopede</t>
+          <t>Scolipede</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Scoliopede</t>
+          <t>Scolipede</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -34111,7 +34111,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Amoongus</t>
+          <t>Amoonguss</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -34131,12 +34131,12 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Amoongus</t>
+          <t>Amoonguss</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Amoongus</t>
+          <t>Amoonguss</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -42319,7 +42319,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Gumchoos</t>
+          <t>Gumshoos</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -42339,12 +42339,12 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>Gumchoos</t>
+          <t>Gumshoos</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>Gumchoos</t>
+          <t>Gumshoos</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -44314,7 +44314,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Palosand</t>
+          <t>Palossand</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -44334,12 +44334,12 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>Palosand</t>
+          <t>Palossand</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>Palosand</t>
+          <t>Palossand</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -46651,7 +46651,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Thwakey</t>
+          <t>Thwackey</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -46671,12 +46671,12 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>Thwakey</t>
+          <t>Thwackey</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Thwakey</t>
+          <t>Thwackey</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Skowvet</t>
+          <t>Skwovet</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -47127,12 +47127,12 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>Skowvet</t>
+          <t>Skwovet</t>
         </is>
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>Skowvet</t>
+          <t>Skwovet</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
@@ -51097,32 +51097,32 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
+          <t>Zamazenta</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>ザマゼンタ</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
           <t>Zamazanta</t>
         </is>
       </c>
-      <c r="C890" t="inlineStr">
-        <is>
-          <t>ザマゼンタ</t>
-        </is>
-      </c>
-      <c r="D890" t="inlineStr">
+      <c r="E890" t="inlineStr">
         <is>
           <t>Zamazanta</t>
         </is>
       </c>
-      <c r="E890" t="inlineStr">
-        <is>
-          <t>Zamazanta</t>
-        </is>
-      </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>Zamazanta</t>
+          <t>Zamazenta</t>
         </is>
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>Zamazanta</t>
+          <t>Zamazenta</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
@@ -52180,7 +52180,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Meowscarda</t>
+          <t>Meowscarada</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -52200,12 +52200,12 @@
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>Meowscarda</t>
+          <t>Meowscarada</t>
         </is>
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>Meowscarda</t>
+          <t>Meowscarada</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
@@ -54517,7 +54517,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>Toadscruel</t>
+          <t>Toedscruel</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -54537,12 +54537,12 @@
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t>Toadscruel</t>
+          <t>Toedscruel</t>
         </is>
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>Toadscruel</t>
+          <t>Toedscruel</t>
         </is>
       </c>
       <c r="H950" t="inlineStr">
